--- a/artfynd/A 12901-2026 artfynd.xlsx
+++ b/artfynd/A 12901-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120281769</v>
+        <v>120281770</v>
       </c>
       <c r="B2" t="n">
-        <v>57485</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,7 +710,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>409683</v>
+        <v>409703</v>
       </c>
       <c r="R2" t="n">
         <v>6739010</v>
@@ -780,16 +775,11 @@
         <v>120281772</v>
       </c>
       <c r="B3" t="n">
-        <v>78561</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120281770</v>
+        <v>120281771</v>
       </c>
       <c r="B4" t="n">
-        <v>78561</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>409703</v>
+        <v>409816</v>
       </c>
       <c r="R4" t="n">
-        <v>6739010</v>
+        <v>6739074</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120281771</v>
+        <v>120281773</v>
       </c>
       <c r="B5" t="n">
-        <v>78297</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>409816</v>
+        <v>409997</v>
       </c>
       <c r="R5" t="n">
-        <v>6739074</v>
+        <v>6739059</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1046,7 +1026,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Lima</t>
+          <t>Malung</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1057,6 +1037,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1080,6 +1065,103 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120281769</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ripfjället, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>409683</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6739010</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12901-2026 artfynd.xlsx
+++ b/artfynd/A 12901-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120281770</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120281772</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120281771</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120281773</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,8 +1187,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120281769</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>